--- a/apps/besc/docs/evolution/blueprint-custos-besc.xlsx
+++ b/apps/besc/docs/evolution/blueprint-custos-besc.xlsx
@@ -10,6 +10,7 @@
   <sheets>
     <sheet name="Linhas de custo" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Cenários" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Cotações recebidas" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="149">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -194,6 +195,9 @@
     <t xml:space="preserve">Faixas de mercado (jul/2026) — ESTIMATIVA a validar por cotação. Regulação em movimento (VASP fev/2026; CVM 88 em reforma). Custódia KMS/HSM são referências usadas pelo toggle da aba Cenários.</t>
   </si>
   <si>
+    <t xml:space="preserve">Fluxo de cotação: quando a proposta de um RFP chegar, substitua Mín/Máx desta aba pelo valor cotado e marque Confiança='cotado', Fonte=&lt;fornecedor&gt;. Registre a proposta na aba 'Cotações recebidas'. Ver o pacote em docs/evolution/rfp/.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Blueprint de custos BESC — calculadora de cenário</t>
   </si>
   <si>
@@ -288,19 +292,197 @@
   </si>
   <si>
     <t xml:space="preserve">• Se o enquadramento cair em VASP/BCB, some capital mínimo R$ 10,8–37,2 mi (provavelmente NÃO se aplica — ver doc 12).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item (linha de custo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Célula (Linhas de custo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faixa atual mín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faixa atual máx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fornecedor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cotado mín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cotado máx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5/D5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uma vez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(EXEMPLO — apague) Fornecedor X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 dias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">escopo 3 contratos, reauditoria inclusa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2/D2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3/D3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parecer de certeza/exigibilidade (por caso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C15/D15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">por processo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4/D4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C12/D12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">por ano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taxa de administração FIDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% a.a. do PL (piso R$/mês)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C7/D7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11/D11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">por mês</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KYC do titular/investidor (por verificação)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C17/D17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">por verificação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C13/D13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C18/D18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">por titular/ano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carimbo de tempo ICP-Brasil (RFC 3161)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pacote por volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custódia de chaves — KMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C19/D19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custódia de chaves — HSM dedicado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C20/D20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFP-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C6/D6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C10/D10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legenda:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Colunas AMARELAS (Fornecedor…Observação) são para preencher quando a proposta chegar. A linha de exemplo (cinza) deve ser apagada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• 'Célula' aponta a célula da aba 'Linhas de custo' a atualizar (mín em C, máx em D). Atualize lá para o total recalcular.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Itens sem célula ('—'): Taxa de adm. FIDC é % do PL (calculada na aba Cenários); Carimbo RFC 3161 não tem linha fixa (custo por volume).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Este pacote de RFPs está em docs/evolution/rfp/ (um arquivo .md por RFP + README).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;R$ &quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="0.00"/>
+    <numFmt numFmtId="168" formatCode="&quot;R$ &quot;#,##0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -363,6 +545,14 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="11"/>
+      <color rgb="FF999999"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -443,8 +633,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -452,11 +646,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -464,35 +658,39 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -504,7 +702,35 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -566,7 +792,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666666"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -760,602 +986,607 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>30000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>150000</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="G2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>150000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>500000</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="G3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="4" t="n">
         <v>100000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>300000</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
         <v>55000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>275000</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="G5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>20000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>80000</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>30000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>120000</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="G7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>7000</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="G8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="4" t="n">
         <v>3000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>8000</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="G9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="4" t="n">
         <v>2500</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>6500</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>13000</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="4" t="n">
         <v>50000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>150000</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="4" t="n">
         <v>8000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>50000</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>15000</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="4" t="n">
         <v>10000</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="G15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="4" t="n">
         <v>350</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="4" t="n">
         <v>6500</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="4" t="n">
         <v>13000</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1377,449 +1608,449 @@
   <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="9" t="n">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="11" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="10" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="12" t="n">
         <v>10000000</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="11" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="B6" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="12" t="n">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="14" t="n">
         <v>5.5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="13" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13" t="s">
+      <c r="C9" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13" t="s">
+      <c r="D9" s="15"/>
+      <c r="E9" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="H9" s="13"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="14" t="s">
+      <c r="F9" s="15"/>
+      <c r="G9" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="H9" s="15"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C10" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="F10" s="14" t="s">
+      <c r="D10" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="H10" s="14" t="s">
+      <c r="F10" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="16" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="H10" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="3" t="n">
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Setup")*('Linhas de custo'!$G$2:$G$20)*('Linhas de custo'!$C$2:$C$20))</f>
         <v>0</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Setup")*('Linhas de custo'!$G$2:$G$20)*('Linhas de custo'!$D$2:$D$20))</f>
         <v>0</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Setup")*('Linhas de custo'!$H$2:$H$20)*('Linhas de custo'!$C$2:$C$20))</f>
         <v>285000</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Setup")*('Linhas de custo'!$H$2:$H$20)*('Linhas de custo'!$D$2:$D$20))</f>
         <v>1125000</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Setup")*('Linhas de custo'!$I$2:$I$20)*('Linhas de custo'!$C$2:$C$20))</f>
         <v>385000</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Setup")*('Linhas de custo'!$I$2:$I$20)*('Linhas de custo'!$D$2:$D$20))</f>
         <v>1425000</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="3" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="4" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <f aca="false">MAX(809,0.0003*$B$5)</f>
         <v>3000</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="4" t="n">
         <f aca="false">MAX(809,0.0003*$B$5)</f>
         <v>3000</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="4" t="n">
         <f aca="false">MAX(809,0.0064*$B$5)</f>
         <v>64000</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="4" t="n">
         <f aca="false">MAX(809,0.0064*$B$5)</f>
         <v>64000</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="3" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Recorrente-mês")*('Linhas de custo'!$G$2:$G$20)*('Linhas de custo'!$C$2:$C$20))</f>
         <v>2000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Recorrente-mês")*('Linhas de custo'!$G$2:$G$20)*('Linhas de custo'!$D$2:$D$20))</f>
         <v>7000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Recorrente-mês")*('Linhas de custo'!$H$2:$H$20)*('Linhas de custo'!$C$2:$C$20))</f>
         <v>9500</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Recorrente-mês")*('Linhas de custo'!$H$2:$H$20)*('Linhas de custo'!$D$2:$D$20))</f>
         <v>34500</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Recorrente-mês")*('Linhas de custo'!$I$2:$I$20)*('Linhas de custo'!$C$2:$C$20))</f>
         <v>9500</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Recorrente-mês")*('Linhas de custo'!$I$2:$I$20)*('Linhas de custo'!$D$2:$D$20))</f>
         <v>34500</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="3" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <f aca="false">IF($B$6="HSM",'Linhas de custo'!$C$20,'Linhas de custo'!$C$19)</f>
         <v>50</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="4" t="n">
         <f aca="false">IF($B$6="HSM",'Linhas de custo'!$D$20,'Linhas de custo'!$D$19)</f>
         <v>300</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="4" t="n">
         <f aca="false">IF($B$6="HSM",'Linhas de custo'!$C$20,'Linhas de custo'!$C$19)</f>
         <v>50</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" s="4" t="n">
         <f aca="false">IF($B$6="HSM",'Linhas de custo'!$D$20,'Linhas de custo'!$D$19)</f>
         <v>300</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="3" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Recorrente-ano")*('Linhas de custo'!$G$2:$G$20)*('Linhas de custo'!$C$2:$C$20))</f>
         <v>0</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Recorrente-ano")*('Linhas de custo'!$G$2:$G$20)*('Linhas de custo'!$D$2:$D$20))</f>
         <v>0</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Recorrente-ano")*('Linhas de custo'!$H$2:$H$20)*('Linhas de custo'!$C$2:$C$20))</f>
         <v>8000</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Recorrente-ano")*('Linhas de custo'!$H$2:$H$20)*('Linhas de custo'!$D$2:$D$20))</f>
         <v>50000</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Recorrente-ano")*('Linhas de custo'!$I$2:$I$20)*('Linhas de custo'!$C$2:$C$20))</f>
         <v>58000</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Recorrente-ano")*('Linhas de custo'!$I$2:$I$20)*('Linhas de custo'!$D$2:$D$20))</f>
         <v>200000</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" s="3" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="4" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="4" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" s="4" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="4" t="n">
         <f aca="false">MAX(96000,0.008*$B$5)</f>
         <v>96000</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" s="4" t="n">
         <f aca="false">MAX(240000,0.02*$B$5)</f>
         <v>240000</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="3" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Por-processo")*('Linhas de custo'!$G$2:$G$20)*('Linhas de custo'!$C$2:$C$20))</f>
         <v>0</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Por-processo")*('Linhas de custo'!$G$2:$G$20)*('Linhas de custo'!$D$2:$D$20))</f>
         <v>0</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Por-processo")*('Linhas de custo'!$H$2:$H$20)*('Linhas de custo'!$C$2:$C$20))</f>
         <v>4272</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Por-processo")*('Linhas de custo'!$H$2:$H$20)*('Linhas de custo'!$D$2:$D$20))</f>
         <v>27358</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Por-processo")*('Linhas de custo'!$I$2:$I$20)*('Linhas de custo'!$C$2:$C$20))</f>
         <v>4272</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" s="4" t="n">
         <f aca="false">SUMPRODUCT(('Linhas de custo'!$B$2:$B$20="Por-processo")*('Linhas de custo'!$I$2:$I$20)*('Linhas de custo'!$D$2:$D$20))</f>
         <v>27358</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="3" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="4" t="n">
         <f aca="false">C17*$B$4</f>
         <v>0</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="4" t="n">
         <f aca="false">D17*$B$4</f>
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="4" t="n">
         <f aca="false">E17*$B$4</f>
         <v>59808</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="4" t="n">
         <f aca="false">F17*$B$4</f>
         <v>383012</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="4" t="n">
         <f aca="false">G17*$B$4</f>
         <v>59808</v>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" s="4" t="n">
         <f aca="false">H17*$B$4</f>
         <v>383012</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" s="15" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="17" t="n">
         <f aca="false">C11+C12+C18+(C13+C14)*12+C15+C16</f>
         <v>24000</v>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="17" t="n">
         <f aca="false">D11+D12+D18+(D13+D14)*12+D15+D16</f>
         <v>84000</v>
       </c>
-      <c r="E20" s="15" t="n">
+      <c r="E20" s="17" t="n">
         <f aca="false">E11+E12+E18+(E13+E14)*12+E15+E16</f>
         <v>470408</v>
       </c>
-      <c r="F20" s="15" t="n">
+      <c r="F20" s="17" t="n">
         <f aca="false">F11+F12+F18+(F13+F14)*12+F15+F16</f>
         <v>1978612</v>
       </c>
-      <c r="G20" s="15" t="n">
+      <c r="G20" s="17" t="n">
         <f aca="false">G11+G12+G18+(G13+G14)*12+G15+G16</f>
         <v>777408</v>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H20" s="17" t="n">
         <f aca="false">H11+H12+H18+(H13+H14)*12+H15+H16</f>
         <v>2729612</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" s="15" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="17" t="n">
         <f aca="false">C13+C14</f>
         <v>2000</v>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="17" t="n">
         <f aca="false">D13+D14</f>
         <v>7000</v>
       </c>
-      <c r="E21" s="15" t="n">
+      <c r="E21" s="17" t="n">
         <f aca="false">E13+E14</f>
         <v>9550</v>
       </c>
-      <c r="F21" s="15" t="n">
+      <c r="F21" s="17" t="n">
         <f aca="false">F13+F14</f>
         <v>34800</v>
       </c>
-      <c r="G21" s="15" t="n">
+      <c r="G21" s="17" t="n">
         <f aca="false">G13+G14</f>
         <v>9550</v>
       </c>
-      <c r="H21" s="15" t="n">
+      <c r="H21" s="17" t="n">
         <f aca="false">H13+H14</f>
         <v>34800</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" s="15" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="17" t="n">
         <f aca="false">(C13+C14)*12+C15+C16</f>
         <v>24000</v>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D22" s="17" t="n">
         <f aca="false">(D13+D14)*12+D15+D16</f>
         <v>84000</v>
       </c>
-      <c r="E22" s="15" t="n">
+      <c r="E22" s="17" t="n">
         <f aca="false">(E13+E14)*12+E15+E16</f>
         <v>122600</v>
       </c>
-      <c r="F22" s="15" t="n">
+      <c r="F22" s="17" t="n">
         <f aca="false">(F13+F14)*12+F15+F16</f>
         <v>467600</v>
       </c>
-      <c r="G22" s="15" t="n">
+      <c r="G22" s="17" t="n">
         <f aca="false">(G13+G14)*12+G15+G16</f>
         <v>268600</v>
       </c>
-      <c r="H22" s="15" t="n">
+      <c r="H22" s="17" t="n">
         <f aca="false">(H13+H14)*12+H15+H16</f>
         <v>857600</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
         <v>88</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1842,4 +2073,569 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="19" t="n">
+        <v>55000</v>
+      </c>
+      <c r="F2" s="19" t="n">
+        <v>275000</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="H2" s="19" t="n">
+        <v>90000</v>
+      </c>
+      <c r="I2" s="19" t="n">
+        <v>90000</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E3" s="21" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F3" s="21" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G3" s="22"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+      <c r="L3" s="22"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" s="21" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F4" s="21" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G4" s="22"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="21" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F5" s="21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G5" s="22"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G6" s="22"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G7" s="22"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G9" s="22"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>13000</v>
+      </c>
+      <c r="G10" s="22"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" s="22"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>55000</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>275000</v>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G13" s="22"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>120</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>350</v>
+      </c>
+      <c r="G14" s="22"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>300</v>
+      </c>
+      <c r="G16" s="22"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" s="21" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F17" s="21" t="n">
+        <v>13000</v>
+      </c>
+      <c r="G17" s="22"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" s="21" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F18" s="21" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G18" s="22"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>6500</v>
+      </c>
+      <c r="G19" s="22"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>